--- a/光伏配储项目/电价数据/2026/俊帆站.xlsx
+++ b/光伏配储项目/电价数据/2026/俊帆站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.33359</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38457</v>
+      </c>
+      <c r="C117" t="n">
+        <v>1.17493</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.41106</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.44694</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.39941</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.42518</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.37349</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.36942</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.34582</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.35637</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.34331</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.34723</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.35395</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.3364</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.35575</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.35339</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.38454</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.36849</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.38739</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.38504</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.39313</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.39281</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.30002</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33431</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.29118</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.30034</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30097</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.31707</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.30722</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.26588</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.28962</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.25093</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.267</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.25597</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.27668</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>0.33998</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.30936</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.07237</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>0.27072</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.17007</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.26332</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.25137</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.256</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.24065</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>0.22809</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.32984</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>0.28656</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.29014</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.30182</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>0.27398</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>0.30458</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.33249</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.36588</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.7887799999999999</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>0.74064</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>1.03717</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.46829</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.53603</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.56149</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.89147</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>1.45662</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.63935</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>1.67839</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.68575</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>1.10745</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>1.22271</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>1.74377</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>1.35221</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>1.25785</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>1.17885</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.72819</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.65277</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.6249</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.53998</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.5576</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.84615</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="E118" t="n">
+        <v>1.15063</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="G118" t="n">
+        <v>1.21979</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.46894</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.49863</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.48243</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.4799</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.45699</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.38518</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.44171</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.36763</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.36511</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.32876</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.32833</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.32842</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.32287</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.32664</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.3381</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.34302</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.41529</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.36238</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.38961</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35438</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.36831</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.33617</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.36269</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44542</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.34225</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.34229</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.35235</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>0.362</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.303</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.29481</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.34847</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.42491</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.64812</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.60939</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.7209800000000001</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.34185</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.31843</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.31214</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.3032</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.53664</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>0.4727</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.39128</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.35566</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.32879</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.58862</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.37373</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.36706</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.8147799999999999</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.5639700000000001</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.65566</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.65518</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>1.62345</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>1.74536</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>1.04197</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>1.71533</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>1.42369</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>1.70015</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>0.7452000000000001</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>1.36559</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>1.06708</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>1.49226</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>1.31847</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>1.62823</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>1.08709</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>1.69071</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.4294</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>1.07833</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>1.06084</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43018</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.41252</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.42524</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.33019</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.36709</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.33313</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.4784</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.46173</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.48322</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.35633</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.4248</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.39858</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.35538</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.37838</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.3712</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.35473</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.40851</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.42094</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.33176</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.36075</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.38106</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.35644</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.34778</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.35234</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.34421</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.33528</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.36561</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.37979</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.44683</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.43105</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.41926</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.34429</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.34726</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.36719</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.34432</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.1547</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.19745</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.26523</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.34854</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.10946</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.67126</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.5726100000000001</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.34037</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>0.56351</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.8091499999999999</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.8091499999999999</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.72388</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.82726</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>0.95938</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>1.04961</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>1.07002</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>1.13182</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.49432</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.50761</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.71229</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.6392599999999999</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.60139</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.57128</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.4846</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.5469299999999999</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.24863</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.45821</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.51151</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.52236</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.58386</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.62675</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.58884</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.64061</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.9361900000000001</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.57298</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.70799</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.45083</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.51203</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.5615399999999999</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.6060599999999999</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>0.69733</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.72257</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.42859</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.6166699999999999</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.40307</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.4677</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.51187</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.65872</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.52149</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.63736</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.56465</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.57782</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.53459</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.7403200000000001</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.42527</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.43912</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.38785</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.36193</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.34556</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.34012</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.31894</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.63093</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.60025</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.50539</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.40923</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.40679</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.4225</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.38305</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.36753</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.42105</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.41732</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.3723</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.51503</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.34284</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.36261</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.36409</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.33367</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.3317</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.329</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.34745</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.35743</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.40932</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.42117</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.39027</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.34083</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.38435</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.45123</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.47273</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.3573</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.44593</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.33895</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.37702</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.34925</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.32829</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.4516</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.35934</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.32993</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.45015</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.48469</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.46859</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.37937</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>0.12899</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>0.2972</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.80435</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.3374</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.3238</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>0.36834</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.37646</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>0.34652</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.37719</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.37657</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.33421</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.09312000000000001</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.38136</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.32814</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.33563</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.37462</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.11139</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.45063</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.364</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.37178</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.42646</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.47177</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.36906</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.67153</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.40472</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.36891</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.50242</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.37723</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.36534</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.3431</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.34332</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.33036</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.33982</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.31669</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.3207</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.31875</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.31173</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.31485</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.30973</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.26531</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.37263</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.35381</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.32793</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.32045</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.31886</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.31582</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.3187</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.31513</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.31679</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.31336</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.31579</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31331</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.31453</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31646</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32452</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32612</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.3198</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.30819</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.32077</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.34438</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.28649</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.31924</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.31413</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>0.31883</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>0.30381</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>0.28973</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>0.32036</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>0.31032</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>0.1436</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>0.31505</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>0.02734</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>0.30341</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>0.29296</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>0.31601</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>0.3201</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>0.30157</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>0.40582</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.26436</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.25729</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.23899</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.10376</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>0.30292</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>0.26602</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>0.03755</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.26352</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.29737</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.29978</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.3081</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.30079</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.30491</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31995</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32957</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.31545</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.33545</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.33571</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.33584</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.32681</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.33849</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.34855</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.34024</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.3507</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34827</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.35043</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.36804</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.43439</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.36327</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.45498</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.34283</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.34966</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.31934</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.39152</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.30656</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.25374</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.25825</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.21175</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.29257</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.29227</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.32931</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.20035</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.23246</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.13116</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.25547</v>
+      </c>
+      <c r="O122" t="n">
+        <v>-0.03851</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.27979</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.30693</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.15638</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.25336</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.22243</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.20084</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.22507</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.18345</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.30723</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.25478</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.27556</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.32393</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.21009</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.27019</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10815</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04686</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.04697999999999999</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04409</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04621</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.04482999999999999</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04398</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>0.32312</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>0.01022</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.20659</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.04946</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>0.27598</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>0.19529</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>0.33668</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04392</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04394</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04574</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.0456</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04561</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04369</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04335</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04549</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04339</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>0.01316</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.0453</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04525</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04538</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04358</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04422</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>0.06074</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>0.05894</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04471</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.04997</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.04985</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.0474</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04790999999999999</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.19975</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14272</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.28993</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.29465</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30454</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29492</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29282</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29328</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.29225</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29677</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29074</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29497</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.26875</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29381</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.30855</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30375</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30221</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31434</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.3429700000000001</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.33725</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.32609</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.33775</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.34057</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.317</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.30386</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.21726</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.3093</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.35721</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.32746</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.30704</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.31463</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30134</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28114</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29442</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.28802</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28084</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27116</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27089</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17236</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.1586</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17092</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1477</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.15943</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.15858</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23612</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.214</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22651</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.26883</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28566</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29075</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.28069</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.2810299999999999</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28043</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27069</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.28091</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32236</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31015</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.3163</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.35894</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.31625</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>0.29728</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.38884</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.37096</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.41391</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.43231</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.33181</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.41843</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.41526</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.3354</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.40241</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.30005</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30095</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29929</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.29998</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15654</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.29427</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.31093</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.31342</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.34627</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30067</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.33082</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.38545</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79098</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6220399999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.783</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.40003</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49797</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.7810199999999999</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92039</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.49456</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9142</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.86287</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.2962</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.35363</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.88749</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.6316000000000001</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.18707</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.8704299999999999</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.66171</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.33083</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.0329</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.7909700000000001</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.57511</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.7729600000000001</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.7775299999999999</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.8767699999999999</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.87386</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.49314</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.39866</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.39987</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.44993</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.20698</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.87883</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55102</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.62183</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.53832</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.49769</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.45581</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42425</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.44216</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.38817</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45268</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.4167</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.39323</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.35412</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.37831</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.3892</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.40046</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.32502</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.37547</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.32639</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.32348</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.32055</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.34744</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.44412</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.36593</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.32658</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.45118</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.51334</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.58801</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.81638</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.36978</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.29758</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.44859</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.30342</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.45729</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.34476</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.6750499999999999</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.87501</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.32691</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.8435900000000001</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.35762</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.29274</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>0.26807</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.38019</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.39978</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27211</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.3091</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.30071</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.40648</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.32161</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.30829</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.31953</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31893</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.30675</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.33924</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.31955</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.29391</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.29591</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.30803</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.30577</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.1879</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.26539</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.26536</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.27966</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.26535</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.28376</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.31008</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.30238</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.29656</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.29578</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.30909</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.30951</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.3143</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.29549</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.32541</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="C125" t="n">
+        <v>0.18506</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.31106</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.31037</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.31577</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.31381</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.31052</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.30739</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.3095</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.3142200000000001</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.30615</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.29652</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.30121</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.30718</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.30256</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.2979</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.28421</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.30614</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.30485</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.29993</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.30084</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.30189</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.29945</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.26947</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.23195</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.29331</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.26559</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.30744</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.30998</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30408</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.23764</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.34857</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28588</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.25282</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.30418</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.28536</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.38169</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.13634</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.45757</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.17922</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.2361</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.17035</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.24714</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>0.27057</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.23213</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.25663</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.25764</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.15837</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.13322</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.13963</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.12834</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.10657</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.14068</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.04524</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.13684</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.08626</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.09955</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.0593</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.09347</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.25385</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.25461</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.20965</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.25162</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.23808</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.25269</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.25455</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.24447</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.2483</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.24764</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.23214</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.25182</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.25524</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.26539</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.26136</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.25677</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.2788</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.25447</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.35199</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.27064</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.24235</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.27525</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.27476</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.255</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.25053</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.25967</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.10158</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.41405</v>
+      </c>
+      <c r="D126" t="n">
+        <v>0.96958</v>
+      </c>
+      <c r="E126" t="n">
+        <v>0.46654</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.36328</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.48467</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.33644</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.1144</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.10523</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.24962</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.28847</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.30691</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.24265</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.24182</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.3023</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.27846</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.29721</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.29292</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.27527</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.34086</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.34161</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.27854</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.27163</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.28648</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.35476</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.28281</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.38525</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.2818</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.25692</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.28647</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.27013</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>0.36143</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.09754</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.15389</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.13974</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.29911</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.26711</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.29741</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.27689</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.11552</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.2482</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.3767</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.2815299999999999</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.21772</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.26928</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.1212</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.2275</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.26106</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.27537</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.30072</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.20364</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.15023</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.26816</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.25514</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.13853</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.17609</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.24289</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.1861</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.27338</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.2776</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.14116</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.27726</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.17324</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.23538</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.29654</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.29271</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.28687</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.29192</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.24264</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.2769</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.25206</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.28881</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.2887</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.28235</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.40568</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.27451</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.5255299999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.28794</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.31441</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.31399</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.32128</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.27735</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.30949</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.28583</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.23977</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.28164</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.21258</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.24511</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.22706</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.21834</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.13846</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.17121</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.19605</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.1635</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.19317</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.14004</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.20623</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.22489</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.22272</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.25545</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.25194</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.05959</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.06587999999999999</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.16434</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.17394</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.24792</v>
+      </c>
+      <c r="W127" t="n">
+        <v>-0.02695</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.07521</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.20018</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>-0.02789</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.11997</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.11759</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.16644</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.23774</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.24233</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.14257</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.25297</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.14541</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.27054</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.08925</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.23959</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.07797</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.15806</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.24748</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.22953</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.25375</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.31233</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.25381</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.28105</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.24619</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.24545</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.23264</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.24037</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.25668</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.28445</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.26818</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.26249</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.2649</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.28532</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.26165</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.2833</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.24954</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.26346</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.28506</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.27593</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.26308</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.28284</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.27695</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28265</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.29991</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.31832</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30549</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.28581</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.289</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.30179</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.30806</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.30391</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.29659</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.28935</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.29125</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.2895</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.29596</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.28915</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.31223</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.29098</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.30416</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.53366</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.31652</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.34139</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.28899</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.29123</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.25535</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.2855</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.29254</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.42971</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.3353</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.32425</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.30318</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.30587</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.30654</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.3263</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.41057</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.38998</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.33439</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.32041</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.30312</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.29932</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.29883</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.30295</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.29841</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.29881</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.30352</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.31346</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.30036</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.30581</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.30378</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.30356</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.29404</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.30376</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.29709</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>0.33251</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>0.28321</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.29246</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.30379</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>0.28568</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.32016</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>0.28595</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>0.28808</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.29925</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>0.297</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>0.281</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.29547</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.28734</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.28006</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>0.28372</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.29532</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>0.2975</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.2967</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>0.29041</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.31333</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>0.29722</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.3003</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.36283</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.33679</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.31567</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.38366</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.51159</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.39974</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.372</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.3411</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.35189</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.45921</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.38026</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.47722</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.64018</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.44719</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.43687</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38396</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.36743</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.45838</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34733</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.38763</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.35373</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.37119</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.29369</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.31859</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.32057</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.32078</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.31157</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.31068</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.36949</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.33891</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.30697</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.29272</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.29697</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.29055</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.29693</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.30042</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.30244</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.31861</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.29832</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.29811</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.31483</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.31028</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.29607</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.3116</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.30711</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.29716</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.29487</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.38912</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31351</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.31713</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.31054</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.29828</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.30731</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.30879</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>1.08527</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.577</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>1.23881</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.50843</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.77422</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.49533</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.47296</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.66032</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.80776</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.30492</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.6272799999999999</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>0.39731</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.98073</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.27878</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.385</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.32455</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.28931</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.30558</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.24399</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.44539</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.37773</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.64481</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.59948</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.58431</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.9721599999999999</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.62848</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.6079199999999999</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.7303999999999999</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.54101</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.68335</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.42177</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.35932</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.32767</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.37275</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.40794</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.45385</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.3983</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.86672</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.68586</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.61876</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>-0.04467</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.39469</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.70038</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.38887</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.35379</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.47835</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.1795</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.34123</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.26633</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.32106</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.29435</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.22816</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.28875</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>-0.03904</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.1709</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.32003</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30751</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.2858</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.38632</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.28407</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.28015</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.283</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.28374</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.20713</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.19901</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.27594</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.2809</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.27763</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.27512</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.27507</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.27707</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.20091</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.1982</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.16374</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.24017</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.29177</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.29494</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.26592</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.19793</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.20358</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.16141</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.21084</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.17741</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.16843</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.20651</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.23117</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.27667</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.30883</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.29421</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.34289</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.2868</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31448</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32863</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31593</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.28317</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>0.25659</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.28171</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.27634</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>0.2795299999999999</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.27452</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.24834</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.27981</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.27317</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.28792</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.28723</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.29584</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.27972</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.26089</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.2704</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.23322</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.25193</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.25875</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.15535</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.27703</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.33782</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.29114</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.29954</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.30845</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.2772</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.29247</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.3122799999999999</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.29672</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.30263</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.2780899999999999</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.29029</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.31792</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.28828</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.33822</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.33013</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.279</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.33132</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.29047</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.33278</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.26653</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.29474</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.33615</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.23537</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.28288</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.15326</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.12851</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.32108</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.24103</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.32068</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.2952</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.32217</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.3222</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.32314</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.28469</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.32117</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.31803</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.00523</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.31881</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.29245</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.28916</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.27731</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.31136</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.31182</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.2881</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.29616</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.28615</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.31138</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.2874</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.28825</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.27686</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.31682</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.28713</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.29316</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.29269</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.30811</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.28383</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.27722</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.28774</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.29559</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.27733</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.28764</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>0.27264</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.30118</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.30808</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31245</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.30653</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.30764</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.30597</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.32898</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31791</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37008</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.30887</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.35967</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.32884</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.32235</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.32347</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.31887</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.30524</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32087</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.32253</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.32305</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.32654</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.32687</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36431</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.32184</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34655</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.31789</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.33055</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.3656</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.33252</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.32803</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.35129</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.52755</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.32692</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.34758</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>1.04012</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>1.03467</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.42562</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.21594</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.33785</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.32215</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.38219</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.3114</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.29946</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.322</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.38293</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.34807</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.32564</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.33383</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.33098</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.33064</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.33381</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.3299</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.31781</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.33076</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.32462</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.31506</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.32791</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.32387</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.31406</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.33159</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.28901</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.33056</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.33186</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.35167</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.32835</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.32297</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.32366</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.3297</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.31993</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.30919</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.41624</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.31916</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.32701</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.31941</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.32839</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.33004</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.3378</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.33184</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.31443</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.31838</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.32819</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.3268</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.3283</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.32399</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.32238</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.32022</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>0.33985</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.33873</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.32706</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>0.33178</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.33626</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.33066</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.34187</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.35444</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.5238400000000001</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.41206</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.34492</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.46979</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.38291</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.32358</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.35115</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.43098</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.7102200000000001</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.50714</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>1.13368</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>1.03989</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>1.1308</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.34601</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>1.35306</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.40225</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.6186200000000001</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.5323</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.77646</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.5621699999999999</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.71421</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.42443</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.3653</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.32355</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.32373</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.34678</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.31971</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.31699</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.3457</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.34585</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.37805</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.35109</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.40438</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.32611</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.32482</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.32494</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.32645</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.32522</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.3666</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.34275</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.34985</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.33157</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.35994</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.3142</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.31644</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.29422</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.30929</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.30127</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.29235</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.30641</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.31184</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.32079</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.32176</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.32059</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.4529</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.49151</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.42984</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.5907</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.6641900000000001</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.74862</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.58316</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.40644</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.31969</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.3352</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.35692</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.3861</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.36476</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.32381</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.50138</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.67247</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>0.40763</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.27203</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.39789</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.4939</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.35135</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.3396</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.34752</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.33522</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.33044</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.24633</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.31938</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.29353</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.31219</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.34046</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34572</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.28696</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.3127200000000001</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.32703</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.32445</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.33433</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.31514</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.32827</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.32562</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.32899</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.34023</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.45753</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.32978</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.41083</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.40625</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.34903</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.43351</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>1.17344</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.87225</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.64436</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.38062</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.34671</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.32937</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.33486</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.3254</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.32802</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.35502</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.32785</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.32847</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.32679</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.40636</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39629</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.32362</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.31822</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.2778</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.29365</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.298</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.31711</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.31279</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.30892</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.32889</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.02054</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.28149</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.28845</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.33175</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.33786</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.2825</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.28946</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.35142</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.29599</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.33328</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.32705</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.32915</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.3269</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.35857</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.32763</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.3345</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.33928</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.35674</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.36497</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.33384</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.33707</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.32945</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>0.64075</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.39244</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.38167</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.42519</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.43403</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.42974</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.42946</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.35626</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.35421</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>0.33451</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.33713</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.33868</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.31418</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31732</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.31166</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.2823</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.29588</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.2911</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.29873</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.31632</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.30801</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38139</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.30852</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.18126</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.36669</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38938</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.32484</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.37999</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.24846</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.17009</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.16691</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.23013</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.21225</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.17505</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.33124</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.25459</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.28198</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.33365</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.27526</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.15445</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.11829</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.16081</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.15274</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.1608</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.17631</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.31325</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.2854100000000001</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.25009</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.22696</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.29277</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.22241</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.1777</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.01914</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.2613</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.01518</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.01544</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.17792</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.00487</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.20869</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.17674</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.01389</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.16682</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.17159</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.20447</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.1691</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.17194</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.17479</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.01276</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.17763</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.01257</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>-0.01107</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.18905</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.1899</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.15894</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.28529</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>-0.0246</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.22251</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.28382</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.24433</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.11359</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.26024</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.31189</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.20588</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.3183</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.31198</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.04957</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.26927</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29132</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.28764</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.00313</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.29428</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.30545</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.33656</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.30622</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.32787</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.31694</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>0.25375</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>0.27862</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.29069</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.29849</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>0.25022</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.28411</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.29846</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.30297</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32335</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.3026</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.29278</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>0.25791</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.27097</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.30122</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.30749</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.31073</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.2804</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.26111</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.28036</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.27342</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.26251</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.22861</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.18705</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.18422</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.25388</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.23374</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.28762</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.25269</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.25077</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.1644</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.17313</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.25291</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.15057</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.26873</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.14352</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.20247</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.23419</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.27784</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.27119</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.27437</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.28457</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.27685</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.0581</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.1926</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.18953</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.26958</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.005059999999999999</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.20834</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.22824</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.22024</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.04749</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>-0.00567</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.0073</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.00729</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.00666</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.00666</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.00704</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.20306</v>
+      </c>
+      <c r="X136" t="n">
+        <v>-0.00626</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.00666</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.00671</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.18368</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>-0.00566</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>-0.00566</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.30633</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.008410000000000001</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.00114</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.24621</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04145</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>-0.00577</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>0.00042</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.04958</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.09584999999999999</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>0.02201</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.03958</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.02192</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.04297</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.04089</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.04861</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.04827</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.02446</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.02935</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.04962</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.04403</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.0496</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.04941</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.01252</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>0.2631</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.04939</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.04961</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.04525999999999999</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.04959</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.04965</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.03947</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>0.17618</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.25061</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.26826</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.26619</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.26814</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.27749</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.008</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.27281</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.28579</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.29337</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.29204</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.28667</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.28332</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.2964</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.30864</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.28829</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.29757</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.31159</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.29674</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.28413</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.31542</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.31268</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.31773</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.31211</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.31187</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.30842</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.30716</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.31509</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.30015</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>0.27403</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.36845</v>
+      </c>
+      <c r="D137" t="n">
+        <v>0.34813</v>
+      </c>
+      <c r="E137" t="n">
+        <v>0.3058999999999999</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.04372</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.28724</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.31236</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.29551</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.28519</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.18109</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.31977</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.17546</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.17995</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.1772</v>
+      </c>
+      <c r="P137" t="n">
+        <v>-0.01238</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.17314</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.1615</v>
+      </c>
+      <c r="S137" t="n">
+        <v>-0.01129</v>
+      </c>
+      <c r="T137" t="n">
+        <v>-0.0424</v>
+      </c>
+      <c r="U137" t="n">
+        <v>-0.04013000000000001</v>
+      </c>
+      <c r="V137" t="n">
+        <v>-0.01422</v>
+      </c>
+      <c r="W137" t="n">
+        <v>-0.01076</v>
+      </c>
+      <c r="X137" t="n">
+        <v>-0.04636999999999999</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.01606</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.01855</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.02295</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.41653</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.20579</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.28137</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.32589</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>-0.01405</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>0.24603</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>-0.02531</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.85939</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.8615900000000001</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.32887</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.36146</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>0.09370000000000001</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.00662</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.25241</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>0.31387</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>0.31828</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>0.31932</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>0.29593</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.29812</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>0.299</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>0.44534</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>0.29699</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>0.29185</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>0.00221</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.29138</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>0.00154</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>0.31639</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.3121</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>0.06866</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>0.30646</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>0.30247</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>0.30672</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>0.30793</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.25453</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.29189</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.4749</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.32033</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.31965</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.33061</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.33511</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.33195</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.32568</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33673</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>1.22478</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.79674</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.48563</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.57313</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>1.41865</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>1.5631</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.50906</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.9586699999999999</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.62314</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>1.32424</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>1.32246</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>1.33168</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>1.52759</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.49471</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.6293200000000001</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.51583</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.36405</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.32476</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.35017</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.31195</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33007</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.36113</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.4018</v>
+      </c>
+      <c r="E138" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.6204400000000001</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.29912</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.27973</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.35891</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.27254</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.20357</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.26462</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.26022</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.25325</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.22309</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.2742</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.21118</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.17842</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.20662</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.17265</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.17545</v>
+      </c>
+      <c r="X138" t="n">
+        <v>-0.0129</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.17198</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.19393</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.24211</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.25033</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.2602</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.29956</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.25795</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.27982</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.31431</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.35698</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.33631</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.33265</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.38314</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.31051</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.33033</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.32869</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29774</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.3129</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.30754</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.31552</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31829</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.30847</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>0.25844</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.31117</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.30233</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.30207</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.32669</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.32034</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31802</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31743</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.32591</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.31183</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.31098</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.31748</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.31812</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.31637</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.31683</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.3156</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.32063</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.31615</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.32039</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.32178</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33145</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.36572</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.45951</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.40286</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.36311</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.34922</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.36551</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.33227</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.31695</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.32376</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.30699</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.33219</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.37486</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.32751</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.32976</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.32607</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3525</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.31212</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.29996</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.29552</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.29582</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.40401</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.39709</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.38451</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.33704</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.33771</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.33481</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.33505</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32625</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.32269</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.31657</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.32811</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.31827</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.31749</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.32367</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.31672</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.30527</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.30497</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.29744</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.30105</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.30319</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.30989</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.31571</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.31065</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.31643</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.31575</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.3223</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.31408</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.31663</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.35763</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.90158</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>0.34194</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.57917</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.38706</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.33233</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.32015</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.3235</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.33301</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.3344</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.31915</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.36473</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.29675</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.33445</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.3303</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.33632</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.32141</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.33442</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.33312</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.3437</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.3251</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.32262</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.32675</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.33114</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.32823</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.33269</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.32198</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.32972</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.3333</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.5975900000000001</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.50038</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.6045</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.28721</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>1.3057</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>1.39264</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.49825</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>0.44984</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.7410599999999999</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>1.15067</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>1.37924</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.52155</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>1.20469</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.48469</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.35905</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.35181</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.42982</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.35647</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.32895</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.35787</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.33469</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.34415</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.33366</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.32948</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.33677</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.331</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.20406</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.32288</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.31108</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.31992</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.32009</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.49164</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.36095</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.3321</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.3262</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.32569</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.31878</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.31839</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.32492</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.32344</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.31659</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.32096</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.32052</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.31756</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.31888</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.31848</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.30848</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.30298</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.30765</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.30293</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.30089</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.29705</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.32279</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.29767</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.30849</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.31391</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.3077</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.33864</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.31819</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33319</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.33131</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.32142</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.36278</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.39098</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.34694</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.35366</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.43461</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.37967</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.34443</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.35667</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33733</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.31048</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.3636</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.41951</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.36756</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.39491</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.35149</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.29262</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.39215</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.36571</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.34373</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31629</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.3367</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.35583</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.33345</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.34154</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.33803</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.32483</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.34417</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.33906</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.34737</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.34792</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.37175</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.41969</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.3708399999999999</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.41106</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.37291</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.3671</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.46731</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.44244</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.99012</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>1.0962</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>1.78117</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>1.17178</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.87418</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>1.31734</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>1.07032</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.69963</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>1.79237</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>1.54656</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>1.8</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>1.41655</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>1.18636</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.952</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.3802</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.53032</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.34065</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.34846</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.32272</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.3245</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.28548</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.33286</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.35324</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.31347</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.33222</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.32248</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.28796</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.29964</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.29334</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.30237</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.32563</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.29326</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.31123</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.31479</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.30483</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30513</v>
+      </c>
+      <c r="S141" t="n">
+        <v>-0.01325</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.29162</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29266</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.32102</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.31607</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.29566</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.287</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35802</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.35863</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.30813</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.30644</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.31574</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.31316</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.32256</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.32533</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.32907</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.33174</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>0.3596</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>0.38429</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>0.3205</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.27502</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>0.43631</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.32838</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>0.5813400000000001</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>0.37104</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>0.35004</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>0.20099</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>0.35554</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>0.33078</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.30055</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>0.32508</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.43599</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.55491</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.35428</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.35197</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.32559</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.2906</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.29325</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.33401</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.29602</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.34255</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.34776</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.32028</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.33356</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.34646</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.3376</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.31911</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.35281</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.84746</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.33951</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.3470299999999999</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.35786</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.35346</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.37205</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.3388</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.35037</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38104</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.35812</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.7980700000000001</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.5881799999999999</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.8141799999999999</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>1.22016</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.57617</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.85745</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.615</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.67818</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.39918</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.40311</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.39092</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.35867</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.35955</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.33119</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.3122</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.32877</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.3429</v>
+      </c>
+      <c r="C142" t="n">
+        <v>1.19926</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.50324</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.6519199999999999</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.5636</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.5382100000000001</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.3599</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.44501</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.38936</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.37339</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.3732799999999999</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.39474</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38306</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.3752799999999999</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.3517</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38125</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.38283</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36115</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.37455</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.37659</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.37777</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.36919</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.37031</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.35964</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.38892</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.34481</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.32743</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.33115</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.3454</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.34668</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.34051</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.33538</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.36159</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.33967</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.37534</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>0.33385</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>0.34965</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>0.33369</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>0.33438</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.41423</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.31619</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>0.32301</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>0.31053</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.38713</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.32031</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>0.3063</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>0.28571</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>0.32193</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.30274</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>0.28229</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>0.30573</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>0.32412</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>0.3266</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.3511</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>0.32329</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>0.35398</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.3424700000000001</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.33241</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.32912</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.34943</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.35898</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.37001</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.36414</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.35714</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.35229</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.345</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.35307</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.37041</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.3417</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.36297</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.35485</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.70582</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>1.00446</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.66504</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.43941</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.55092</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.63517</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.47182</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.35854</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.33772</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.33904</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.34011</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.33985</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.34842</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.37202</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.36888</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.31231</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.37209</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.35996</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35768</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.34413</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.34483</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.34114</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.3448</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.33777</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.34165</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.34851</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.32091</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.35656</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.34595</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.33877</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.33043</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.33121</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.33168</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.3373</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33478</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.33703</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.32662</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.3314</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.33434</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.33198</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.3308</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.30599</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.31851</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.30985</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.17607</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.30464</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.29568</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.14573</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.19862</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.14602</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.2876</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.04755</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.12156</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.33323</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.22595</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.26025</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.14404</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.14524</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.18828</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.2268</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.27139</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.15877</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.36211</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.30874</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.16623</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.3034</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.31275</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.20215</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.28118</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.30542</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.31255</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.32532</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.32261</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.32</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.32302</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.33025</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.35436</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.35785</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.37582</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.37992</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.38362</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33243</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.35205</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.32195</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.32799</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.36494</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.38094</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.36508</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.37936</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.38032</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.38308</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.39868</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.38647</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.38088</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.37476</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.36333</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.36152</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.36963</v>
       </c>
     </row>
   </sheetData>
